--- a/p6_deployment/data/spain/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/spain/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,853 +448,853 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YPfVUbHr</t>
+          <t>bDmOFmNG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6VKSvcjS</t>
+          <t>2R3LeSVp</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bTa7XEr2</t>
+          <t>hCtXDRiT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>b5HKtJLF</t>
+          <t>GUi3KB8o</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QF1aZzEk</t>
+          <t>txwTE7xN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jyvFGzK9</t>
+          <t>0IHg08NT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2FcKfgcj</t>
+          <t>jmpGH9h4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t6dOgDCd</t>
+          <t>KMlKGT7A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>b1sNEElM</t>
+          <t>CdoCIkwb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhtRDY3S</t>
+          <t>UXe7JVNi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>URxJFfZF</t>
+          <t>t2MJmVwO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>8ClAHG43</t>
+          <t>vmuNnkgU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>rZIg9hCq</t>
+          <t>4A6T7YOu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>zgRNeZsp</t>
+          <t>r15X6hvn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ptdKHyM0</t>
+          <t>CzAy6Cgh</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>f9p6Idkc</t>
+          <t>ng2l3AwB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>j3vHarqI</t>
+          <t>Ykbp4jO4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>pQwLb2bO</t>
+          <t>tG1h2UhH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>d0sPcMDU</t>
+          <t>K60d1l8N</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>0E7ZHPbn</t>
+          <t>jR8u5W8b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>MN8VI5qt</t>
+          <t>p8EMBsQD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>UmCwHqEh</t>
+          <t>vBRzlvY6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>464jEsbB</t>
+          <t>IaVbhgPh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>j30nFNr5</t>
+          <t>MXyjfFft</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6kcGIH6f</t>
+          <t>4dRfgZ9n</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8vBsG3Tb</t>
+          <t>8lOBki9B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bT3fD1DH</t>
+          <t>CMU2iDva</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>dtJsoqUO</t>
+          <t>I1QvmbmD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>8Krd46Un</t>
+          <t>nuNFlBOH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>CCuD0OTB</t>
+          <t>jDT6jXg5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>3.00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>zRUYn5aC</t>
+          <t>pljua4t8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Gpn42paa</t>
+          <t>AVZJiMYs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>IkKwnPEI</t>
+          <t>lMYNjtll</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>MNn03Qqg</t>
+          <t>tGPbjCx8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>On7P9S6P</t>
+          <t>dOgqbOeE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Qegi5nFt</t>
+          <t>2PQfihN1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>OQ7BJcil</t>
+          <t>jogmcrBK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>fyo814E5</t>
+          <t>rqYRk03f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>z3nnd9xQ</t>
+          <t>dnxWlKI0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1306,562 +1306,562 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>SnnhzSF6</t>
+          <t>Uyhid2QQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>xITrckNJ</t>
+          <t>roPPwZh2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrZDiTps</t>
+          <t>CzYsffwq</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>dMjdZoVC</t>
+          <t>YkMjhY7e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>lASMk7Fg</t>
+          <t>UsLLvFwd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>S0RQlRUa</t>
+          <t>thsCaGFL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>WYXHjm0m</t>
+          <t>zuCB1xo9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Quk8Kwxr</t>
+          <t>21r80d0F</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>MNQUmop6</t>
+          <t>zFtGbzVR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>zDk0Y5pJ</t>
+          <t>faNngEhk</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>6Xcqxlof</t>
+          <t>dlD72IV2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SQAHNlW0</t>
+          <t>YF5sRe9d</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>b7fyvAGs</t>
+          <t>AXlQkunc</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>802tPJTQ</t>
+          <t>8SWCty9q</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Ak0MM8o7</t>
+          <t>romYmJG9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>db89rj8Q</t>
+          <t>lOmUla13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>GniCqWhK</t>
+          <t>xptsncoM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hUguwUVm</t>
+          <t>fLjxmwWF</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Oh4QLS0D</t>
+          <t>fP6wSyfj</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>xdh8pCwE</t>
+          <t>GzuooH0S</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>ldmly800</t>
+          <t>nJVGueOk</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>GOhPpLXd</t>
+          <t>OtG7XcWS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>6gBYNcQq</t>
+          <t>f1Sfz0nA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>K079PA1l</t>
+          <t>GATjytX3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>lzCDOUGf</t>
+          <t>SlmdFbAp</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>0GAxNHuj</t>
+          <t>YovnxMHc</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1871,1141 +1871,1141 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>lxiXra29</t>
+          <t>tIQ2YwHM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>0CfyrJHF</t>
+          <t>2RRbZJ1G</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>v79tMyed</t>
+          <t>027ZSHvp</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>tA85Qjnr</t>
+          <t>Krzrw22i</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>fFiTqum3</t>
+          <t>6un0EIPj</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>U93xQaEK</t>
+          <t>KQO7ykRn</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>nVydAvdp</t>
+          <t>ttDGZSea</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>EsHfVuY9</t>
+          <t>YZkkJ7BI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>ziIjWLI3</t>
+          <t>CvURWQuI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hSSoX13c</t>
+          <t>bHNBz9tg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>CY8XQuaE</t>
+          <t>vRVJYnB5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>vPOsYsli</t>
+          <t>jiK3xVBt</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>QLz09bBj</t>
+          <t>YmVNX6QB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>UXJ6SwIS</t>
+          <t>nwfgIRQO</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>8IVcUamG</t>
+          <t>lrYysB3P</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>6yfTEKmT</t>
+          <t>YiLZl50A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>n9U1TJ2M</t>
+          <t>KAzpM9Ra</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>EsVk11JT</t>
+          <t>tKytNkCg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>h800L44o</t>
+          <t>ncxxOVdm</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>j3MHdLRp</t>
+          <t>0MisLTt6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>vP2CI2l4</t>
+          <t>SCe5TiZP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>KKVo2s4N</t>
+          <t>063J5lsJ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>YsATRLq8</t>
+          <t>vDjoKmdC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>SpePF0YM</t>
+          <t>MF4F6URC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>Wba4KOJi</t>
+          <t>YgYXOBss</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MmhHHM3A</t>
+          <t>lMd1UXJJ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>0Y38JrZc</t>
+          <t>YPfVUbHr</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>YNeLGtJG</t>
+          <t>6VKSvcjS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MRGt5qK4</t>
+          <t>bTa7XEr2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>2NqGlOZN</t>
+          <t>b5HKtJLF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>S4Hx6P4b</t>
+          <t>QF1aZzEk</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>tUWs3NlH</t>
+          <t>jyvFGzK9</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>E1DY65kh</t>
+          <t>2FcKfgcj</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>0IFp43ZA</t>
+          <t>t6dOgDCd</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hnPP8RKu</t>
+          <t>b1sNEElM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>WxOT7ozn</t>
+          <t>xhtRDY3S</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>KvMo3x77</t>
+          <t>URxJFfZF</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>KbfBk4KH</t>
+          <t>8ClAHG43</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>tErKmrkU</t>
+          <t>rZIg9hCq</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bBpme8jt</t>
+          <t>zgRNeZsp</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>WOregnLh</t>
+          <t>ptdKHyM0</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MDy8jp5B</t>
+          <t>f9p6Idkc</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>4AhZ4O27</t>
+          <t>j3vHarqI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>dpgV54m1</t>
+          <t>pQwLb2bO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>Sjx4iQk5</t>
+          <t>d0sPcMDU</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>6yIs4Ii1</t>
+          <t>0E7ZHPbn</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>nZHJCzMD</t>
+          <t>MN8VI5qt</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hYqifS5n</t>
+          <t>UmCwHqEh</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>l0w0h6za</t>
+          <t>464jEsbB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>r1iw4rID</t>
+          <t>j30nFNr5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>MRvmgR3e</t>
+          <t>6kcGIH6f</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>zV4M7QIl</t>
+          <t>8vBsG3Tb</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3015,156 +3015,156 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>MR0I863r</t>
+          <t>bT3fD1DH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>8KKsF8QE</t>
+          <t>dtJsoqUO</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>QeFnESuL</t>
+          <t>8Krd46Un</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>4nEjDneR</t>
+          <t>CCuD0OTB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>GQXei5Y7</t>
+          <t>zRUYn5aC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>UTLwGlB8</t>
+          <t>Gpn42paa</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>OCSx5bxe</t>
+          <t>IkKwnPEI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3176,64 +3176,2066 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>IgfR6pYf</t>
+          <t>MNn03Qqg</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>4jUihoJ1</t>
+          <t>On7P9S6P</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
+          <t>Qegi5nFt</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>OQ7BJcil</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>fyo814E5</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>z3nnd9xQ</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>SnnhzSF6</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>xITrckNJ</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>hrZDiTps</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>dMjdZoVC</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>lASMk7Fg</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>S0RQlRUa</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>WYXHjm0m</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>Quk8Kwxr</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>MNQUmop6</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>zDk0Y5pJ</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>6Xcqxlof</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>SQAHNlW0</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>b7fyvAGs</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>802tPJTQ</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>Ak0MM8o7</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>db89rj8Q</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>GniCqWhK</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>hUguwUVm</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>Oh4QLS0D</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>xdh8pCwE</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>ldmly800</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>GOhPpLXd</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>6gBYNcQq</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>K079PA1l</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>lzCDOUGf</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>0GAxNHuj</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>lxiXra29</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>0CfyrJHF</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>v79tMyed</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>tA85Qjnr</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>fFiTqum3</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>U93xQaEK</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>nVydAvdp</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>EsHfVuY9</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>ziIjWLI3</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>hSSoX13c</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>CY8XQuaE</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>vPOsYsli</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>QLz09bBj</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>UXJ6SwIS</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>8IVcUamG</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>6yfTEKmT</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>n9U1TJ2M</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>EsVk11JT</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>h800L44o</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>j3MHdLRp</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>vP2CI2l4</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>KKVo2s4N</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>YsATRLq8</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>SpePF0YM</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>Wba4KOJi</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>MmhHHM3A</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>0Y38JrZc</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>YNeLGtJG</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>MRGt5qK4</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>2NqGlOZN</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>S4Hx6P4b</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>tUWs3NlH</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>E1DY65kh</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>0IFp43ZA</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>hnPP8RKu</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>WxOT7ozn</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>KvMo3x77</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>KbfBk4KH</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>tErKmrkU</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>bBpme8jt</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>WOregnLh</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>MDy8jp5B</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>4AhZ4O27</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>dpgV54m1</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>Sjx4iQk5</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>6yIs4Ii1</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>nZHJCzMD</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>hYqifS5n</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>l0w0h6za</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>r1iw4rID</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>MRvmgR3e</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>zV4M7QIl</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>MR0I863r</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>8KKsF8QE</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>QeFnESuL</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>4nEjDneR</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>GQXei5Y7</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>UTLwGlB8</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>OCSx5bxe</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>IgfR6pYf</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>4jUihoJ1</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
           <t>fDGKB9JI</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>5.25</t>
         </is>
